--- a/TestData/LV_2_CF_TMTT0049771_VerifyTheCAOAndNonCAOCFGroupAndCAOMAAndOrCAOCSPermissionSetsHasModifiedInternalTeamAccessOnEngagementWithERPMAAndOrCS.xlsx
+++ b/TestData/LV_2_CF_TMTT0049771_VerifyTheCAOAndNonCAOCFGroupAndCAOMAAndOrCAOCSPermissionSetsHasModifiedInternalTeamAccessOnEngagementWithERPMAAndOrCS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6821F7-DE04-45BE-9C93-DBDE0CCB8014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE6BB6D-12AB-47B8-9D9B-63145BF11EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUsers" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="99">
   <si>
     <t>User</t>
   </si>
@@ -332,6 +332,15 @@
   </si>
   <si>
     <t>Christopher Lescinsky</t>
+  </si>
+  <si>
+    <t>Anthony Forshaw</t>
+  </si>
+  <si>
+    <t>James Craven</t>
+  </si>
+  <si>
+    <t>Product Specialty</t>
   </si>
 </sst>
 </file>
@@ -1056,27 +1065,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
